--- a/XYZ_Bank_Digital_Business_Executive_Brief_FY2024.xlsx
+++ b/XYZ_Bank_Digital_Business_Executive_Brief_FY2024.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Science\Digital Banking Project\Executive Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A84BF2C1-D9F7-4E94-BD44-F21BA0F40B2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D76B39A-FEB8-4394-AAC4-BD65F4A470E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{0E7C3FA9-47BA-4504-B032-3ED0B2A2A6FB}"/>
   </bookViews>
@@ -279,9 +279,6 @@
     </r>
   </si>
   <si>
-    <t>Launch a dedicated SME digital engagement programme targeting the 116 churned SME customers. Offer tailored digital banking features — bulk payments, payroll, supplier management — that address SME-specific pain points. A 30% re-engagement rate would recover approximately KSh 47M in SME transaction value alone.</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -318,9 +315,6 @@
     </r>
   </si>
   <si>
-    <t>Target the 410 dormant activated customers with a time-limited reactivation campaign — push notifications, fee waivers on next 3 transactions, or airtime incentives. Dormant customers already know the platform, reducing reactivation cost significantly compared to acquiring new customers. Revenue at risk: KSh 394M.</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -375,7 +369,13 @@
     <t>4.  Conduct deeper cohort analysis on SME and Mass Affluent churn to identify specific product friction points — Q2 2025.</t>
   </si>
   <si>
-    <t>XYZ Bank — Internal Document  |  Analysis conducted using MySQL · Python · Tableau Public  |  Data: Digital Customers FY 2024  |  Benard Musyoka Mwinzi</t>
+    <t>Launch a dedicated SME digital engagement programme targeting the 116 churned SME customers. Offer tailored digital banking features like bulk payments, payroll, and supplier management to address SME-specific pain points. A 30% re-engagement rate would recover approximately KSh 47M in SME transaction value alone.</t>
+  </si>
+  <si>
+    <t>Target the 410 dormant activated customers with a time-limited reactivation campaign like push notifications, fee waivers on next 3 transactions, or airtime incentives. Dormant customers already know the platform, reducing reactivation cost significantly compared to acquiring new customers. Revenue at risk: KSh 394M.</t>
+  </si>
+  <si>
+    <t>XYZ Bank — Internal Document  |  Analysis conducted using MySQL · Python · Tableau  |  Data: Digital Customers FY 2024  |  Benard Musyoka Mwinzi</t>
   </si>
 </sst>
 </file>
@@ -518,42 +518,42 @@
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -879,7 +879,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DD392D6-10FA-4237-94C5-EC8C6A679765}">
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.6328125" customWidth="1"/>
@@ -894,23 +894,23 @@
     <row r="1" spans="1:6" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:6" ht="35" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
       <c r="F2" s="1"/>
     </row>
     <row r="3" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4"/>
-      <c r="B3" s="3" t="s">
+      <c r="A3" s="2"/>
+      <c r="B3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="4"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:6" ht="8" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
@@ -921,213 +921,225 @@
       <c r="F4" s="1"/>
     </row>
     <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="6"/>
-      <c r="B5" s="5" t="s">
+      <c r="A5" s="3"/>
+      <c r="B5" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="6"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:6" ht="46" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="8"/>
-      <c r="B6" s="7" t="s">
+      <c r="A6" s="4"/>
+      <c r="B6" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="8"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="4"/>
     </row>
     <row r="7" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
     </row>
     <row r="8" spans="1:6" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="6"/>
-      <c r="B9" s="9" t="s">
+      <c r="A9" s="3"/>
+      <c r="B9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="6"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1"/>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
       <c r="F10" s="1"/>
     </row>
     <row r="11" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="8"/>
-      <c r="B11" s="12" t="s">
+      <c r="A11" s="4"/>
+      <c r="B11" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="8"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="4"/>
     </row>
     <row r="12" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1"/>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
       <c r="F12" s="1"/>
     </row>
     <row r="13" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="8"/>
-      <c r="B13" s="12" t="s">
+      <c r="A13" s="4"/>
+      <c r="B13" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="8"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="4"/>
     </row>
     <row r="14" spans="1:6" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="6"/>
-      <c r="B15" s="13" t="s">
+      <c r="A15" s="3"/>
+      <c r="B15" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="6"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="3"/>
     </row>
     <row r="16" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
       <c r="F16" s="1"/>
     </row>
     <row r="17" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="15"/>
-      <c r="B17" s="14" t="s">
+      <c r="A17" s="8"/>
+      <c r="B17" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="15"/>
+      <c r="C17" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="8"/>
     </row>
     <row r="18" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="1"/>
+    </row>
+    <row r="19" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="4"/>
+      <c r="B19" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C19" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="1"/>
-    </row>
-    <row r="19" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="8"/>
-      <c r="B19" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="8"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="4"/>
     </row>
     <row r="20" spans="1:6" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="6"/>
-      <c r="B21" s="9" t="s">
+      <c r="A21" s="3"/>
+      <c r="B21" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="3"/>
+    </row>
+    <row r="22" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="4"/>
+      <c r="B22" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="8"/>
+      <c r="B23" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="6"/>
-    </row>
-    <row r="22" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="8"/>
-      <c r="B22" s="11" t="s">
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="8"/>
+    </row>
+    <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="4"/>
+      <c r="B24" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="8"/>
-    </row>
-    <row r="23" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="15"/>
-      <c r="B23" s="11" t="s">
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="4"/>
+    </row>
+    <row r="25" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B25" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="15"/>
-    </row>
-    <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="8"/>
-      <c r="B24" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="8"/>
-    </row>
-    <row r="25" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
     </row>
     <row r="26" spans="1:6" ht="4" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="27" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="8"/>
-      <c r="B27" s="16" t="s">
+      <c r="A27" s="4"/>
+      <c r="B27" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="8"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="C16:E16"/>
     <mergeCell ref="B25:E25"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="C18:E18"/>
@@ -1136,18 +1148,6 @@
     <mergeCell ref="B22:E22"/>
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B24:E24"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="C10:E10"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
